--- a/docs/downloads/12/tbl_pro1_alaotra_tous.xlsx
+++ b/docs/downloads/12/tbl_pro1_alaotra_tous.xlsx
@@ -362,47 +362,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
     </row>
